--- a/03_process_editions/Metadata/Mailings.xlsx
+++ b/03_process_editions/Metadata/Mailings.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vanniejo\Documents_local\01_dataplatform\021_SVbevraging\01_code\02_process_editions\Metadata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vanniejo\Documents_local\01_dataplatform\021_SVbevraging\01_code\03_process_editions\Metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB6BCBE8-A916-4597-B99F-DC0C9E49BFB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E9B0C93-5D6C-49F5-94AE-77E0F3E17B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3960" yWindow="17172" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="zendingen" sheetId="1" r:id="rId1"/>
@@ -22,61 +22,61 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="19">
   <si>
-    <t xml:space="preserve">SV1     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">uitnodiging             </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1ste herinnering        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2de herinnering         </t>
-  </si>
-  <si>
-    <t>schriftelijke afsluiting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">online afsluiting       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SV2-SV3 </t>
-  </si>
-  <si>
     <t xml:space="preserve">rechtzetting            </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SV4     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SV5-SV6 </t>
-  </si>
-  <si>
-    <t>SV7</t>
-  </si>
-  <si>
-    <t>SV8-SV9</t>
-  </si>
-  <si>
-    <t>SV10</t>
-  </si>
-  <si>
-    <t>SV13</t>
-  </si>
-  <si>
-    <t>SV11-SV12</t>
-  </si>
-  <si>
-    <t>SV14-SV15</t>
   </si>
   <si>
     <t>fw_period</t>
   </si>
   <si>
-    <t>mailing</t>
+    <t>date</t>
   </si>
   <si>
-    <t>date</t>
+    <t>invitation</t>
+  </si>
+  <si>
+    <t>reminder_1</t>
+  </si>
+  <si>
+    <t>reminder_2</t>
+  </si>
+  <si>
+    <t>closing_paper</t>
+  </si>
+  <si>
+    <t>closing_online</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SV0001     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SV0002-SV0003 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SV0004     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SV0005-SV0006 </t>
+  </si>
+  <si>
+    <t>SV0007</t>
+  </si>
+  <si>
+    <t>SV0008-SV0009</t>
+  </si>
+  <si>
+    <t>SV0010</t>
+  </si>
+  <si>
+    <t>SV0011-SV0012</t>
+  </si>
+  <si>
+    <t>SV0013</t>
+  </si>
+  <si>
+    <t>SV0014-SV0015</t>
+  </si>
+  <si>
+    <t>contact</t>
   </si>
 </sst>
 </file>
@@ -918,598 +918,583 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" customWidth="1"/>
-    <col min="2" max="2" width="26.140625" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" customWidth="1"/>
+    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" t="s">
-        <v>18</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1">
+        <v>44221</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C3" s="1">
-        <v>44221</v>
+        <v>44228</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C4" s="1">
-        <v>44228</v>
+        <v>44249</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1">
-        <v>44249</v>
+        <v>44267</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C6" s="1">
-        <v>44267</v>
+        <v>44272</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>44272</v>
+        <v>44502</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C8" s="1"/>
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1">
+        <v>44508</v>
+      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C9" s="1">
-        <v>44502</v>
+        <v>44529</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C10" s="1">
-        <v>44508</v>
+        <v>44547</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
         <v>6</v>
       </c>
-      <c r="B11" t="s">
-        <v>3</v>
-      </c>
       <c r="C11" s="1">
-        <v>44529</v>
+        <v>44578</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B12" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="1">
-        <v>44547</v>
+        <v>44578</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13" s="1">
-        <v>44578</v>
+        <v>44697</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="1">
+        <v>44711</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="1">
-        <v>44578</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C15" s="1"/>
+      <c r="C15" s="1">
+        <v>44725</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C16" s="1">
-        <v>44697</v>
+        <v>44756</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C17" s="1">
-        <v>44711</v>
+        <v>44760</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
         <v>3</v>
       </c>
       <c r="C18" s="1">
-        <v>44725</v>
+        <v>44879</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
         <v>4</v>
       </c>
       <c r="C19" s="1">
-        <v>44756</v>
+        <v>44893</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
         <v>5</v>
       </c>
       <c r="C20" s="1">
-        <v>44760</v>
+        <v>44907</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C21" s="1"/>
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="1">
+        <v>44935</v>
+      </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C22" s="1">
-        <v>44879</v>
+        <v>44945</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C23" s="1">
-        <v>44893</v>
+        <v>45014</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" s="1">
-        <v>44907</v>
+        <v>45028</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" s="1">
-        <v>44935</v>
+        <v>45056</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C26" s="1">
-        <v>44945</v>
+        <v>45117</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C27" s="1"/>
+      <c r="A27" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="1">
+        <v>45117</v>
+      </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C28" s="1">
-        <v>45014</v>
+        <v>45215</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C29" s="1">
-        <v>45028</v>
+        <v>45229</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B30" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C30" s="1">
-        <v>45056</v>
+        <v>45252</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C31" s="1">
-        <v>45117</v>
+        <v>45293</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B32" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C32" s="1">
-        <v>45117</v>
+        <v>45303</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C33" s="1"/>
+      <c r="A33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="1">
+        <v>45364</v>
+      </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B34" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C34" s="1">
-        <v>45215</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B35" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C35" s="1">
-        <v>45229</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B36" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C36" s="1">
-        <v>45252</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B37" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C37" s="1">
-        <v>45293</v>
+        <v>45451</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B38" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C38" s="1">
-        <v>45303</v>
+        <v>45588</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" s="1">
+        <v>45609</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B40" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C40" s="1">
-        <v>45364</v>
+        <v>45637</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B41" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C41" s="1">
-        <v>45378</v>
+        <v>45665</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B42" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C42" s="1">
-        <v>45406</v>
+        <v>45665</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B43" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C43" s="1">
-        <v>45453</v>
+        <v>45733</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C44" s="1">
+        <v>45747</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>16</v>
+      </c>
+      <c r="B45" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="1">
-        <v>45451</v>
+      <c r="C45" s="1">
+        <v>45769</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B46" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C46" s="1">
-        <v>45588</v>
+        <v>46026</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B47" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C47" s="1">
-        <v>45609</v>
+        <v>45810</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B48" t="s">
         <v>3</v>
       </c>
       <c r="C48" s="1">
-        <v>45637</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B49" t="s">
         <v>4</v>
       </c>
       <c r="C49" s="1">
-        <v>45665</v>
+        <v>45966</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B50" t="s">
         <v>5</v>
       </c>
       <c r="C50" s="1">
-        <v>45665</v>
+        <v>45987</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B51" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="1">
+        <v>46026</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B52" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C52" s="1">
-        <v>45733</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>13</v>
-      </c>
-      <c r="B53" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="1">
-        <v>45747</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>13</v>
-      </c>
-      <c r="B54" t="s">
-        <v>3</v>
-      </c>
-      <c r="C54" s="1">
-        <v>45769</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>13</v>
-      </c>
-      <c r="B55" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="1">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>13</v>
-      </c>
-      <c r="B56" t="s">
-        <v>5</v>
-      </c>
-      <c r="C56" s="1">
-        <v>45810</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>1</v>
-      </c>
-      <c r="C58" s="1">
-        <v>45952</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="1">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>3</v>
-      </c>
-      <c r="C60" s="1">
-        <v>45987</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>4</v>
-      </c>
-      <c r="C61" s="1">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>5</v>
-      </c>
-      <c r="C62" s="1">
         <v>46010</v>
       </c>
     </row>
@@ -1520,6 +1505,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ff9b9dd8-fcc8-4df5-a108-c5866d1d7b9b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="9a9ec0f0-7796-43d0-ac1f-4c8c46ee0bd1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A6AD3661E8CB194C8675B85DE5B2CF8E" ma:contentTypeVersion="18" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="74052aabd80d88734f9eb511f320c0f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ff9b9dd8-fcc8-4df5-a108-c5866d1d7b9b" xmlns:ns3="5b0c7779-fcdd-4d12-9999-ca37719676af" xmlns:ns4="9a9ec0f0-7796-43d0-ac1f-4c8c46ee0bd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c4265b27bfda865713f908aeb805a5eb" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="ff9b9dd8-fcc8-4df5-a108-c5866d1d7b9b"/>
@@ -1767,27 +1772,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E10744E6-C15B-437A-8DAF-8929EFDAAA80}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ff9b9dd8-fcc8-4df5-a108-c5866d1d7b9b"/>
+    <ds:schemaRef ds:uri="9a9ec0f0-7796-43d0-ac1f-4c8c46ee0bd1"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ff9b9dd8-fcc8-4df5-a108-c5866d1d7b9b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="9a9ec0f0-7796-43d0-ac1f-4c8c46ee0bd1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9205C066-4BCD-4020-8F81-C9330B381DA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{604A710D-D5C5-4188-B49C-BAA64AB5B146}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1805,23 +1809,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9205C066-4BCD-4020-8F81-C9330B381DA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E10744E6-C15B-437A-8DAF-8929EFDAAA80}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ff9b9dd8-fcc8-4df5-a108-c5866d1d7b9b"/>
-    <ds:schemaRef ds:uri="9a9ec0f0-7796-43d0-ac1f-4c8c46ee0bd1"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>